--- a/artfynd/A 14592-2025 artfynd.xlsx
+++ b/artfynd/A 14592-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125081276</v>
+        <v>125081336</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571604</v>
+        <v>571601</v>
       </c>
       <c r="R2" t="n">
-        <v>6427044</v>
+        <v>6427068</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125081336</v>
+        <v>125081276</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571601</v>
+        <v>571604</v>
       </c>
       <c r="R5" t="n">
-        <v>6427068</v>
+        <v>6427044</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 14592-2025 artfynd.xlsx
+++ b/artfynd/A 14592-2025 artfynd.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sven Halling</t>
+          <t>Sven Halling, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sven Halling</t>
+          <t>Sven Halling, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 14592-2025 artfynd.xlsx
+++ b/artfynd/A 14592-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125081336</v>
+        <v>125081276</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571601</v>
+        <v>571604</v>
       </c>
       <c r="R2" t="n">
-        <v>6427068</v>
+        <v>6427044</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125081411</v>
+        <v>125081336</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571577</v>
+        <v>571601</v>
       </c>
       <c r="R3" t="n">
-        <v>6427062</v>
+        <v>6427068</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1001,14 +1001,14 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sven Halling, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sven Halling</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125081276</v>
+        <v>125081411</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571604</v>
+        <v>571577</v>
       </c>
       <c r="R5" t="n">
-        <v>6427044</v>
+        <v>6427062</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sven Halling, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sven Halling</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 14592-2025 artfynd.xlsx
+++ b/artfynd/A 14592-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125081276</v>
+        <v>125081248</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571604</v>
+        <v>571606</v>
       </c>
       <c r="R2" t="n">
-        <v>6427044</v>
+        <v>6427053</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125081248</v>
+        <v>125081411</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571606</v>
+        <v>571577</v>
       </c>
       <c r="R4" t="n">
-        <v>6427053</v>
+        <v>6427062</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125081411</v>
+        <v>125081276</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571577</v>
+        <v>571604</v>
       </c>
       <c r="R5" t="n">
-        <v>6427062</v>
+        <v>6427044</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 14592-2025 artfynd.xlsx
+++ b/artfynd/A 14592-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125081248</v>
+        <v>125081276</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571606</v>
+        <v>571604</v>
       </c>
       <c r="R2" t="n">
-        <v>6427053</v>
+        <v>6427044</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125081336</v>
+        <v>125081248</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571601</v>
+        <v>571606</v>
       </c>
       <c r="R3" t="n">
-        <v>6427068</v>
+        <v>6427053</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125081411</v>
+        <v>125081336</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571577</v>
+        <v>571601</v>
       </c>
       <c r="R4" t="n">
-        <v>6427062</v>
+        <v>6427068</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125081276</v>
+        <v>125081411</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571604</v>
+        <v>571577</v>
       </c>
       <c r="R5" t="n">
-        <v>6427044</v>
+        <v>6427062</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 14592-2025 artfynd.xlsx
+++ b/artfynd/A 14592-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125081276</v>
+        <v>125081248</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571604</v>
+        <v>571606</v>
       </c>
       <c r="R2" t="n">
-        <v>6427044</v>
+        <v>6427053</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125081248</v>
+        <v>125081336</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571606</v>
+        <v>571601</v>
       </c>
       <c r="R3" t="n">
-        <v>6427053</v>
+        <v>6427068</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125081336</v>
+        <v>125081276</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571601</v>
+        <v>571604</v>
       </c>
       <c r="R4" t="n">
-        <v>6427068</v>
+        <v>6427044</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 14592-2025 artfynd.xlsx
+++ b/artfynd/A 14592-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125081248</v>
+        <v>125081276</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571606</v>
+        <v>571604</v>
       </c>
       <c r="R2" t="n">
-        <v>6427053</v>
+        <v>6427044</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125081336</v>
+        <v>125081411</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571601</v>
+        <v>571577</v>
       </c>
       <c r="R3" t="n">
-        <v>6427068</v>
+        <v>6427062</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125081276</v>
+        <v>125081248</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571604</v>
+        <v>571606</v>
       </c>
       <c r="R4" t="n">
-        <v>6427044</v>
+        <v>6427053</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125081411</v>
+        <v>125081336</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571577</v>
+        <v>571601</v>
       </c>
       <c r="R5" t="n">
-        <v>6427062</v>
+        <v>6427068</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 14592-2025 artfynd.xlsx
+++ b/artfynd/A 14592-2025 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125081411</v>
+        <v>125081248</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571577</v>
+        <v>571606</v>
       </c>
       <c r="R3" t="n">
-        <v>6427062</v>
+        <v>6427053</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125081248</v>
+        <v>125081336</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571606</v>
+        <v>571601</v>
       </c>
       <c r="R4" t="n">
-        <v>6427053</v>
+        <v>6427068</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125081336</v>
+        <v>125081411</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571601</v>
+        <v>571577</v>
       </c>
       <c r="R5" t="n">
-        <v>6427068</v>
+        <v>6427062</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 14592-2025 artfynd.xlsx
+++ b/artfynd/A 14592-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125081276</v>
+        <v>125081248</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571604</v>
+        <v>571606</v>
       </c>
       <c r="R2" t="n">
-        <v>6427044</v>
+        <v>6427053</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125081248</v>
+        <v>125081411</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571606</v>
+        <v>571577</v>
       </c>
       <c r="R3" t="n">
-        <v>6427053</v>
+        <v>6427062</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,7 +900,7 @@
         <v>125081336</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125081411</v>
+        <v>125081276</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571577</v>
+        <v>571604</v>
       </c>
       <c r="R5" t="n">
-        <v>6427062</v>
+        <v>6427044</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 14592-2025 artfynd.xlsx
+++ b/artfynd/A 14592-2025 artfynd.xlsx
@@ -779,14 +779,14 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sven Halling</t>
+          <t>Sven Halling, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125081411</v>
+        <v>125081336</v>
       </c>
       <c r="B3" t="n">
         <v>98269</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571577</v>
+        <v>571601</v>
       </c>
       <c r="R3" t="n">
-        <v>6427062</v>
+        <v>6427068</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125081336</v>
+        <v>125081411</v>
       </c>
       <c r="B4" t="n">
         <v>98269</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571601</v>
+        <v>571577</v>
       </c>
       <c r="R4" t="n">
-        <v>6427068</v>
+        <v>6427062</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sven Halling</t>
+          <t>Sven Halling, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 14592-2025 artfynd.xlsx
+++ b/artfynd/A 14592-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125081248</v>
+        <v>125081411</v>
       </c>
       <c r="B2" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571606</v>
+        <v>571577</v>
       </c>
       <c r="R2" t="n">
-        <v>6427053</v>
+        <v>6427062</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -779,22 +774,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sven Halling, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sven Halling</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125081336</v>
+        <v>125081248</v>
       </c>
       <c r="B3" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -834,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571601</v>
+        <v>571606</v>
       </c>
       <c r="R3" t="n">
-        <v>6427068</v>
+        <v>6427053</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125081411</v>
+        <v>125081276</v>
       </c>
       <c r="B4" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571577</v>
+        <v>571604</v>
       </c>
       <c r="R4" t="n">
-        <v>6427062</v>
+        <v>6427044</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125081276</v>
+        <v>125081336</v>
       </c>
       <c r="B5" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1056,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571604</v>
+        <v>571601</v>
       </c>
       <c r="R5" t="n">
-        <v>6427044</v>
+        <v>6427068</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1112,7 +1092,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sven Halling, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sven Halling</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
